--- a/data/trans_orig/P1423-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1423-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de depresión o ansiedad en 2007</t>
+          <t>Población con diagnóstico de depresión o ansiedad en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18385</t>
+          <t>18791</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9330</t>
+          <t>9051</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24308</t>
+          <t>24603</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17490</t>
+          <t>18125</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37748</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>455391</t>
+          <t>454985</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>468177</t>
+          <t>468098</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>282372</t>
+          <t>282077</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>297350</t>
+          <t>297629</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>742709</t>
+          <t>742187</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>762967</t>
+          <t>762332</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>3489</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15930</t>
+          <t>15537</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13988</t>
+          <t>14485</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>33748</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20430</t>
+          <t>21138</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42424</t>
+          <t>41527</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>351004</t>
+          <t>351397</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>362916</t>
+          <t>363445</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>339294</t>
+          <t>338117</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>357877</t>
+          <t>357380</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>696375</t>
+          <t>697272</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>718369</t>
+          <t>717661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12657</t>
+          <t>12334</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30917</t>
+          <t>29176</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10432</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26840</t>
+          <t>27352</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26042</t>
+          <t>27363</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50879</t>
+          <t>51347</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>511472</t>
+          <t>513213</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>529732</t>
+          <t>530055</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140942</t>
+          <t>140430</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157350</t>
+          <t>157546</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>659292</t>
+          <t>658824</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>684129</t>
+          <t>682808</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27365</t>
+          <t>29214</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52087</t>
+          <t>53182</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43892</t>
+          <t>42266</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73833</t>
+          <t>72481</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>80121</t>
+          <t>79434</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118040</t>
+          <t>116013</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1186247</t>
+          <t>1185152</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1210969</t>
+          <t>1209120</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>640452</t>
+          <t>641804</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>670393</t>
+          <t>672019</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1834580</t>
+          <t>1836607</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1872499</t>
+          <t>1873186</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9574</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25653</t>
+          <t>26609</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40291</t>
+          <t>40081</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68186</t>
+          <t>67355</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52675</t>
+          <t>54845</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86195</t>
+          <t>86711</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>324902</t>
+          <t>323946</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>340981</t>
+          <t>340234</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>500566</t>
+          <t>501397</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>528461</t>
+          <t>528671</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>833112</t>
+          <t>832596</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>866632</t>
+          <t>864462</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14441</t>
+          <t>14924</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>74170</t>
+          <t>70041</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>111553</t>
+          <t>109908</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79043</t>
+          <t>80638</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>117838</t>
+          <t>118225</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>283760</t>
+          <t>283277</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>294911</t>
+          <t>295319</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1137207</t>
+          <t>1138852</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1174590</t>
+          <t>1178719</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1429122</t>
+          <t>1428735</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1467917</t>
+          <t>1466322</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>83536</t>
+          <t>82149</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>122928</t>
+          <t>123034</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>223911</t>
+          <t>224139</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>283791</t>
+          <t>287667</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>321391</t>
+          <t>323350</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>395583</t>
+          <t>397896</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3147262</t>
+          <t>3147156</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3186654</t>
+          <t>3188041</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3094333</t>
+          <t>3090457</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3154213</t>
+          <t>3153985</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6252731</t>
+          <t>6250418</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6326923</t>
+          <t>6324964</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,14%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de depresión o ansiedad en 2012</t>
+          <t>Población con diagnóstico de depresión o ansiedad en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21105</t>
+          <t>20517</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>7708</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25895</t>
+          <t>23787</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16920</t>
+          <t>17542</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40938</t>
+          <t>39465</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>416106</t>
+          <t>416694</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>430996</t>
+          <t>431065</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>288559</t>
+          <t>290667</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>306390</t>
+          <t>306746</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>710727</t>
+          <t>712200</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>734745</t>
+          <t>734123</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>7138</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23998</t>
+          <t>24390</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11258</t>
+          <t>12067</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29641</t>
+          <t>29878</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21766</t>
+          <t>21192</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46975</t>
+          <t>45324</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>394799</t>
+          <t>394407</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>411768</t>
+          <t>411659</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>308370</t>
+          <t>308133</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>326753</t>
+          <t>325944</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>709833</t>
+          <t>711484</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>735042</t>
+          <t>735616</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30836</t>
+          <t>29839</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57619</t>
+          <t>57032</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27194</t>
+          <t>27786</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49921</t>
+          <t>49091</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64158</t>
+          <t>62307</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100314</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,04%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>571796</t>
+          <t>572383</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>598579</t>
+          <t>599576</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>210208</t>
+          <t>211038</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>232935</t>
+          <t>232343</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>789230</t>
+          <t>791350</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>825386</t>
+          <t>827237</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>93,0%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41344</t>
+          <t>39519</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>73479</t>
+          <t>70815</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65270</t>
+          <t>67438</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101637</t>
+          <t>103569</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>117681</t>
+          <t>116151</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>163785</t>
+          <t>162637</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1085530</t>
+          <t>1088194</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1117665</t>
+          <t>1119490</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>663085</t>
+          <t>661153</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>699452</t>
+          <t>697284</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1759946</t>
+          <t>1761094</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1806050</t>
+          <t>1807580</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10637</t>
+          <t>10006</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26217</t>
+          <t>26304</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>94576</t>
+          <t>94967</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>133570</t>
+          <t>135625</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>109402</t>
+          <t>110585</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>153910</t>
+          <t>155573</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>484379</t>
+          <t>484292</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>499959</t>
+          <t>500590</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>626676</t>
+          <t>624621</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>665670</t>
+          <t>665279</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1116933</t>
+          <t>1115270</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1161441</t>
+          <t>1160258</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,3%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5995</t>
+          <t>6340</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>117037</t>
+          <t>115841</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>162148</t>
+          <t>159271</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>118187</t>
+          <t>115340</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>162120</t>
+          <t>160304</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>260887</t>
+          <t>260542</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>947203</t>
+          <t>950080</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>992314</t>
+          <t>993510</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1214113</t>
+          <t>1215929</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1258046</t>
+          <t>1260893</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,62%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>117353</t>
+          <t>116039</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>168315</t>
+          <t>168701</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>367185</t>
+          <t>370279</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>442653</t>
+          <t>443386</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>495732</t>
+          <t>502844</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>593642</t>
+          <t>598488</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3253595</t>
+          <t>3253209</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3304557</t>
+          <t>3305871</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3104262</t>
+          <t>3103529</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3179730</t>
+          <t>3176636</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6375183</t>
+          <t>6370337</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6473093</t>
+          <t>6465981</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de depresión o ansiedad en 2016</t>
+          <t>Población con diagnóstico de depresión o ansiedad en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5674</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20077</t>
+          <t>20168</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10280</t>
+          <t>9903</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28613</t>
+          <t>27403</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18345</t>
+          <t>18196</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41094</t>
+          <t>40243</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>409015</t>
+          <t>408924</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>423418</t>
+          <t>423297</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>318442</t>
+          <t>319652</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>336775</t>
+          <t>337152</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>735053</t>
+          <t>735904</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>757802</t>
+          <t>757951</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>3697</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15722</t>
+          <t>15952</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9235</t>
+          <t>9241</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26070</t>
+          <t>25377</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>15514</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35532</t>
+          <t>35819</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>361505</t>
+          <t>361275</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>373238</t>
+          <t>373530</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>346203</t>
+          <t>346896</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>363038</t>
+          <t>363032</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>713968</t>
+          <t>713681</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>733399</t>
+          <t>733986</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12647</t>
+          <t>12932</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31417</t>
+          <t>31094</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15002</t>
+          <t>14552</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34168</t>
+          <t>34194</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31143</t>
+          <t>32132</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57982</t>
+          <t>59672</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>490497</t>
+          <t>490820</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>509267</t>
+          <t>508982</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131955</t>
+          <t>131929</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151121</t>
+          <t>151571</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>630054</t>
+          <t>628364</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>656893</t>
+          <t>655904</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,33%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28407</t>
+          <t>28093</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53891</t>
+          <t>53933</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55480</t>
+          <t>56609</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90041</t>
+          <t>89912</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92195</t>
+          <t>91313</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132723</t>
+          <t>133375</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1095747</t>
+          <t>1095705</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1121231</t>
+          <t>1121545</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>735835</t>
+          <t>735964</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>770396</t>
+          <t>769267</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1842791</t>
+          <t>1842139</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1883319</t>
+          <t>1884201</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17039</t>
+          <t>16778</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36579</t>
+          <t>36743</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>94042</t>
+          <t>92628</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>133665</t>
+          <t>131701</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>115999</t>
+          <t>116108</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>163286</t>
+          <t>162841</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>584127</t>
+          <t>583963</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>603667</t>
+          <t>603928</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>604579</t>
+          <t>606543</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>644202</t>
+          <t>645616</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1195664</t>
+          <t>1196109</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1242951</t>
+          <t>1242842</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>952</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9181</t>
+          <t>9717</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>101030</t>
+          <t>103771</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>144577</t>
+          <t>146162</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>106959</t>
+          <t>106591</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>151134</t>
+          <t>150136</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>277964</t>
+          <t>277428</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286191</t>
+          <t>286193</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>937448</t>
+          <t>935863</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>980995</t>
+          <t>978254</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1218036</t>
+          <t>1219034</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1262211</t>
+          <t>1262579</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,21%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91575</t>
+          <t>89592</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>133619</t>
+          <t>132190</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>321787</t>
+          <t>325621</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>401676</t>
+          <t>401272</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>427812</t>
+          <t>429476</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>518275</t>
+          <t>517282</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3252103</t>
+          <t>3253532</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3294147</t>
+          <t>3296130</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3129920</t>
+          <t>3130324</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3209809</t>
+          <t>3205975</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6399043</t>
+          <t>6400036</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6489506</t>
+          <t>6487842</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,79%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de depresión o ansiedad en 2023</t>
+          <t>Población con diagnóstico de depresión o ansiedad en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15079</t>
+          <t>14738</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33846</t>
+          <t>35004</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25765</t>
+          <t>26419</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44478</t>
+          <t>45402</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46313</t>
+          <t>46205</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72593</t>
+          <t>72919</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>471366</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>490133</t>
+          <t>490474</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>402989</t>
+          <t>402065</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>421702</t>
+          <t>421048</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>880086</t>
+          <t>879760</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>906366</t>
+          <t>906474</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18015</t>
+          <t>17633</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37011</t>
+          <t>37579</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29892</t>
+          <t>29412</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51923</t>
+          <t>50280</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51819</t>
+          <t>50447</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81131</t>
+          <t>79993</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415202</t>
+          <t>414634</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>434198</t>
+          <t>434580</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>330657</t>
+          <t>332300</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>352688</t>
+          <t>353168</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>753662</t>
+          <t>754800</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>782974</t>
+          <t>784346</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>11519</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56281</t>
+          <t>57600</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16534</t>
+          <t>16279</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29265</t>
+          <t>29326</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22193</t>
+          <t>23835</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82560</t>
+          <t>81613</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>611983</t>
+          <t>610664</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>657383</t>
+          <t>656745</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137646</t>
+          <t>137585</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>150377</t>
+          <t>150632</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>752615</t>
+          <t>753562</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>812982</t>
+          <t>811340</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48568</t>
+          <t>47634</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78074</t>
+          <t>77481</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43312</t>
+          <t>51319</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>119230</t>
+          <t>120947</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108655</t>
+          <t>103682</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>178270</t>
+          <t>177334</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>956745</t>
+          <t>957338</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>986251</t>
+          <t>987185</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>858864</t>
+          <t>857147</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>934782</t>
+          <t>926775</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1834642</t>
+          <t>1835578</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1904257</t>
+          <t>1909230</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,85%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26936</t>
+          <t>25908</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49241</t>
+          <t>49339</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>91151</t>
+          <t>95441</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>147836</t>
+          <t>149448</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>132700</t>
+          <t>130469</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>185939</t>
+          <t>189039</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>425805</t>
+          <t>425707</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>448110</t>
+          <t>449138</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>693499</t>
+          <t>691887</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>750184</t>
+          <t>745894</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1130442</t>
+          <t>1127342</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1183681</t>
+          <t>1185912</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,09%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27472</t>
+          <t>28562</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>79591</t>
+          <t>80141</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112735</t>
+          <t>111810</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>91257</t>
+          <t>90295</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>127364</t>
+          <t>129723</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>213035</t>
+          <t>211945</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>234340</t>
+          <t>233782</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>648636</t>
+          <t>649561</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>681780</t>
+          <t>681230</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>874514</t>
+          <t>872155</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>910621</t>
+          <t>911583</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,99%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>145780</t>
+          <t>148802</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>224933</t>
+          <t>223314</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>334593</t>
+          <t>331557</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>446955</t>
+          <t>449010</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>510437</t>
+          <t>514345</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>654685</t>
+          <t>647704</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3151127</t>
+          <t>3152746</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3230280</t>
+          <t>3227258</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3130803</t>
+          <t>3128748</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3243165</t>
+          <t>3246201</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6299133</t>
+          <t>6306114</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6443381</t>
+          <t>6439473</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1423-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1423-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>5583</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18791</t>
+          <t>19354</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9051</t>
+          <t>8638</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24603</t>
+          <t>24384</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18125</t>
+          <t>17722</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>37395</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>454985</t>
+          <t>454422</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>468098</t>
+          <t>468193</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>282077</t>
+          <t>282296</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>297629</t>
+          <t>298042</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>742187</t>
+          <t>743062</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>762332</t>
+          <t>762735</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15537</t>
+          <t>15437</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14485</t>
+          <t>14384</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33748</t>
+          <t>32599</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21138</t>
+          <t>20948</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41527</t>
+          <t>42940</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>351397</t>
+          <t>351497</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363445</t>
+          <t>363314</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>338117</t>
+          <t>339266</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>357380</t>
+          <t>357481</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>697272</t>
+          <t>695859</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>717661</t>
+          <t>717851</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12334</t>
+          <t>13045</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29176</t>
+          <t>30017</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10236</t>
+          <t>10622</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27352</t>
+          <t>27654</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27363</t>
+          <t>27718</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51347</t>
+          <t>53003</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>513213</t>
+          <t>512372</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>530055</t>
+          <t>529344</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140430</t>
+          <t>140128</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157546</t>
+          <t>157160</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>658824</t>
+          <t>657168</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>682808</t>
+          <t>682453</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,1%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29214</t>
+          <t>28123</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53182</t>
+          <t>51099</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42266</t>
+          <t>44738</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72481</t>
+          <t>73934</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79434</t>
+          <t>78563</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>116013</t>
+          <t>117278</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1185152</t>
+          <t>1187235</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1209120</t>
+          <t>1210211</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>641804</t>
+          <t>640351</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>672019</t>
+          <t>669547</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1836607</t>
+          <t>1835342</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1873186</t>
+          <t>1874057</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>9775</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26609</t>
+          <t>25165</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40081</t>
+          <t>38718</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67355</t>
+          <t>67971</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54845</t>
+          <t>54277</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>86711</t>
+          <t>85623</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>323946</t>
+          <t>325390</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>340234</t>
+          <t>340780</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>501397</t>
+          <t>500781</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>528671</t>
+          <t>530034</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>832596</t>
+          <t>833684</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>864462</t>
+          <t>865030</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14924</t>
+          <t>14542</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>70041</t>
+          <t>73077</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>109908</t>
+          <t>109605</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>80638</t>
+          <t>78988</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>118225</t>
+          <t>118780</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>283277</t>
+          <t>283659</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>295319</t>
+          <t>295269</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1138852</t>
+          <t>1139155</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1178719</t>
+          <t>1175683</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1428735</t>
+          <t>1428180</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1466322</t>
+          <t>1467972</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,89%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>82149</t>
+          <t>84011</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>123034</t>
+          <t>124907</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>224139</t>
+          <t>227628</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>287667</t>
+          <t>286568</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>323350</t>
+          <t>320777</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>397896</t>
+          <t>394750</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3147156</t>
+          <t>3145283</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3188041</t>
+          <t>3186179</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3090457</t>
+          <t>3091556</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3153985</t>
+          <t>3150496</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6250418</t>
+          <t>6253564</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6324964</t>
+          <t>6327537</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20517</t>
+          <t>22348</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7708</t>
+          <t>8973</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23787</t>
+          <t>25542</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17542</t>
+          <t>17474</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39465</t>
+          <t>39803</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>416694</t>
+          <t>414863</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>431065</t>
+          <t>430382</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>290667</t>
+          <t>288912</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>306746</t>
+          <t>305481</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>712200</t>
+          <t>711862</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>734123</t>
+          <t>734191</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7138</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24390</t>
+          <t>24819</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12067</t>
+          <t>11335</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29878</t>
+          <t>29113</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21192</t>
+          <t>22188</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45324</t>
+          <t>47584</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>394407</t>
+          <t>393978</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>411659</t>
+          <t>411636</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>308133</t>
+          <t>308898</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>325944</t>
+          <t>326676</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>711484</t>
+          <t>709224</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>735616</t>
+          <t>734620</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29839</t>
+          <t>30799</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57032</t>
+          <t>56607</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27786</t>
+          <t>28481</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49091</t>
+          <t>51073</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62307</t>
+          <t>63291</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98194</t>
+          <t>99684</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>572383</t>
+          <t>572808</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>599576</t>
+          <t>598616</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>211038</t>
+          <t>209056</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>232343</t>
+          <t>231648</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>791350</t>
+          <t>789860</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>827237</t>
+          <t>826253</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,88%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39519</t>
+          <t>40860</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70815</t>
+          <t>73547</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67438</t>
+          <t>67154</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>103569</t>
+          <t>100903</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>116151</t>
+          <t>116069</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>162637</t>
+          <t>162771</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1088194</t>
+          <t>1085462</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1119490</t>
+          <t>1118149</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>661153</t>
+          <t>663819</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>697284</t>
+          <t>697568</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1761094</t>
+          <t>1760960</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1807580</t>
+          <t>1807662</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10006</t>
+          <t>10123</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26304</t>
+          <t>26428</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>94967</t>
+          <t>94936</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>135625</t>
+          <t>136093</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>110585</t>
+          <t>109980</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155573</t>
+          <t>153456</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>484292</t>
+          <t>484168</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>500590</t>
+          <t>500473</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>624621</t>
+          <t>624153</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>665279</t>
+          <t>665310</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1115270</t>
+          <t>1117387</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1160258</t>
+          <t>1160863</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,35%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6514</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>115841</t>
+          <t>115469</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>159271</t>
+          <t>160355</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>115340</t>
+          <t>117592</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>160304</t>
+          <t>160943</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>260542</t>
+          <t>260368</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>950080</t>
+          <t>948996</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>993510</t>
+          <t>993882</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1215929</t>
+          <t>1215290</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1260893</t>
+          <t>1258641</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,46%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>116039</t>
+          <t>117376</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>168701</t>
+          <t>169843</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>370279</t>
+          <t>368875</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>443386</t>
+          <t>447206</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>502844</t>
+          <t>500913</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>598488</t>
+          <t>593610</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3253209</t>
+          <t>3252067</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3305871</t>
+          <t>3304534</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3103529</t>
+          <t>3099709</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3176636</t>
+          <t>3178040</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6370337</t>
+          <t>6375215</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6465981</t>
+          <t>6467912</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,81%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20168</t>
+          <t>19839</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9903</t>
+          <t>9388</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27403</t>
+          <t>27195</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18196</t>
+          <t>19142</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40243</t>
+          <t>41469</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>408924</t>
+          <t>409253</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>423297</t>
+          <t>423812</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>319652</t>
+          <t>319860</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>337152</t>
+          <t>337667</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>735904</t>
+          <t>734678</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>757951</t>
+          <t>757005</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15952</t>
+          <t>16207</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9241</t>
+          <t>8557</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25377</t>
+          <t>24922</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15514</t>
+          <t>15885</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35819</t>
+          <t>36915</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>361275</t>
+          <t>361020</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>373530</t>
+          <t>373377</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>346896</t>
+          <t>347351</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>363032</t>
+          <t>363716</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>713681</t>
+          <t>712585</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>733986</t>
+          <t>733615</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12932</t>
+          <t>13066</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31094</t>
+          <t>30605</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14552</t>
+          <t>14635</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34194</t>
+          <t>34419</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32132</t>
+          <t>31820</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59672</t>
+          <t>58823</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>490820</t>
+          <t>491309</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>508982</t>
+          <t>508848</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131929</t>
+          <t>131704</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>151571</t>
+          <t>151488</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>628364</t>
+          <t>629213</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>655904</t>
+          <t>656216</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28093</t>
+          <t>28806</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53933</t>
+          <t>54889</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56609</t>
+          <t>57315</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89912</t>
+          <t>87864</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91313</t>
+          <t>92356</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133375</t>
+          <t>134289</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1095705</t>
+          <t>1094749</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1121545</t>
+          <t>1120832</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>735964</t>
+          <t>738012</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>769267</t>
+          <t>768561</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1842139</t>
+          <t>1841225</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1884201</t>
+          <t>1883158</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16778</t>
+          <t>17652</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36743</t>
+          <t>37101</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>92628</t>
+          <t>94251</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>131701</t>
+          <t>131620</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>116108</t>
+          <t>116954</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>162841</t>
+          <t>160541</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>583963</t>
+          <t>583605</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>603928</t>
+          <t>603054</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>606543</t>
+          <t>606624</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>645616</t>
+          <t>643993</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1196109</t>
+          <t>1198409</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1242842</t>
+          <t>1241996</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,39%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>956</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9717</t>
+          <t>9641</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>103771</t>
+          <t>104163</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>146162</t>
+          <t>145683</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>106591</t>
+          <t>107299</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>150136</t>
+          <t>151044</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>277428</t>
+          <t>277504</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>286193</t>
+          <t>286189</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>935863</t>
+          <t>936342</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>978254</t>
+          <t>977862</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1219034</t>
+          <t>1218126</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1262579</t>
+          <t>1261871</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>89592</t>
+          <t>91934</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>132190</t>
+          <t>134336</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>325621</t>
+          <t>324602</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>401272</t>
+          <t>396854</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>429476</t>
+          <t>429311</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>517282</t>
+          <t>517923</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3253532</t>
+          <t>3251386</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3296130</t>
+          <t>3293788</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3130324</t>
+          <t>3134742</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3205975</t>
+          <t>3206994</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6400036</t>
+          <t>6399395</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6487842</t>
+          <t>6488007</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>23037</t>
+          <t>23736</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14738</t>
+          <t>15569</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35004</t>
+          <t>34091</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>34847</t>
+          <t>39646</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26419</t>
+          <t>31370</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45402</t>
+          <t>52246</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>57883</t>
+          <t>63382</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46205</t>
+          <t>50190</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72919</t>
+          <t>78832</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>482175</t>
+          <t>526882</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>470208</t>
+          <t>516527</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>490474</t>
+          <t>535049</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>412620</t>
+          <t>448765</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>402065</t>
+          <t>436165</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>421048</t>
+          <t>457041</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>894796</t>
+          <t>975647</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>879760</t>
+          <t>960197</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>906474</t>
+          <t>988839</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25994</t>
+          <t>28446</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17633</t>
+          <t>19565</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37579</t>
+          <t>40687</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38878</t>
+          <t>41994</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29412</t>
+          <t>31744</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50280</t>
+          <t>54337</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,17 +9046,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>64871</t>
+          <t>70440</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50447</t>
+          <t>56354</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79993</t>
+          <t>88683</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>426219</t>
+          <t>454766</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>414634</t>
+          <t>442525</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>434580</t>
+          <t>463647</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>343702</t>
+          <t>381149</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>332300</t>
+          <t>368806</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>353168</t>
+          <t>391399</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,17 +9159,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>769922</t>
+          <t>835915</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>754800</t>
+          <t>817672</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>784346</t>
+          <t>850001</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,78%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>32366</t>
+          <t>34272</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11519</t>
+          <t>23799</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57600</t>
+          <t>45976</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>22054</t>
+          <t>24557</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16279</t>
+          <t>18262</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29326</t>
+          <t>33063</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>54419</t>
+          <t>58829</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23835</t>
+          <t>45853</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81613</t>
+          <t>73880</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>635898</t>
+          <t>437340</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>610664</t>
+          <t>425636</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>656745</t>
+          <t>447813</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>144857</t>
+          <t>162940</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137585</t>
+          <t>154434</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>150632</t>
+          <t>169235</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>780756</t>
+          <t>600280</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>753562</t>
+          <t>585229</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>811340</t>
+          <t>613256</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>61257</t>
+          <t>68332</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47634</t>
+          <t>53841</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77481</t>
+          <t>86742</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>89550</t>
+          <t>100233</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51319</t>
+          <t>85434</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>120947</t>
+          <t>117054</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>150807</t>
+          <t>168565</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103682</t>
+          <t>146756</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177334</t>
+          <t>191829</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>973562</t>
+          <t>1063511</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>957338</t>
+          <t>1045101</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>987185</t>
+          <t>1078002</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>888544</t>
+          <t>760978</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>857147</t>
+          <t>744157</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>926775</t>
+          <t>775777</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1862105</t>
+          <t>1824489</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1835578</t>
+          <t>1801225</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1909230</t>
+          <t>1846298</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>92,64%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>36327</t>
+          <t>38503</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25908</t>
+          <t>27488</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49339</t>
+          <t>52612</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>126106</t>
+          <t>138615</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>95441</t>
+          <t>123701</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>149448</t>
+          <t>157346</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>162433</t>
+          <t>177118</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>130469</t>
+          <t>155759</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>189039</t>
+          <t>198144</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>438719</t>
+          <t>529461</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>425707</t>
+          <t>515352</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>449138</t>
+          <t>540476</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>715229</t>
+          <t>692235</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>691887</t>
+          <t>673504</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>745894</t>
+          <t>707149</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1153948</t>
+          <t>1221696</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1127342</t>
+          <t>1200670</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1185912</t>
+          <t>1243055</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>88,86%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13299</t>
+          <t>15189</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6725</t>
+          <t>7652</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28562</t>
+          <t>28591</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>94052</t>
+          <t>102985</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>80141</t>
+          <t>87198</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>111810</t>
+          <t>120394</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>107350</t>
+          <t>118174</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>90295</t>
+          <t>99872</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>129723</t>
+          <t>142373</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>227208</t>
+          <t>222039</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>211945</t>
+          <t>208637</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>233782</t>
+          <t>229576</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>667319</t>
+          <t>741296</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>649561</t>
+          <t>723887</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>681230</t>
+          <t>757083</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>894528</t>
+          <t>963335</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>872155</t>
+          <t>939136</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>911583</t>
+          <t>981637</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,77%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>192278</t>
+          <t>208479</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>148802</t>
+          <t>181493</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>223314</t>
+          <t>240130</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>405486</t>
+          <t>448030</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>331557</t>
+          <t>414142</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>449010</t>
+          <t>484415</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>597764</t>
+          <t>656509</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>514345</t>
+          <t>610150</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>647704</t>
+          <t>699055</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3183782</t>
+          <t>3233997</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3152746</t>
+          <t>3202346</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3227258</t>
+          <t>3260983</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3172272</t>
+          <t>3187363</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3128748</t>
+          <t>3150978</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3246201</t>
+          <t>3221251</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6356054</t>
+          <t>6421360</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6306114</t>
+          <t>6378814</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6439473</t>
+          <t>6467719</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
